--- a/branches/feat/temp-card/ValueSet-mii-vs-biobank-biosafety-level-snomedct.xlsx
+++ b/branches/feat/temp-card/ValueSet-mii-vs-biobank-biosafety-level-snomedct.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:00:58+00:00</t>
+    <t>2026-09-10T12:12:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
